--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/ago-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/ago-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/ago-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/ago-2026.xlsx
@@ -5780,7 +5780,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/ago-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/ago-2026.xlsx
@@ -684,7 +684,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +871,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1119,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1184,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1249,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2046,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2294,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2420,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3156,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3770,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4750,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4815,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5185,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5311,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +5925,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6478,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/ago-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/ago-2026.xlsx
@@ -936,7 +936,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1375,7 +1379,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1558,7 +1566,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2359,7 +2371,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2607,7 +2623,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3034,7 +3054,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3587,7 +3611,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4201,7 +4229,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4628,7 +4660,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4689,7 +4725,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6726,7 +6766,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7031,7 +7075,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7092,7 +7140,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/ago-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/ago-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M109"/>
+  <dimension ref="A1:M112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -973,7 +973,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1057402-8542-CM26</t>
+          <t>1057539-6536-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3517,37 +3517,37 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3557,13 +3557,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3980.3</v>
+        <v>3583.75</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1549-3602-CM26</t>
+          <t>1057402-8542-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3588,47 +3588,43 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>73577.87</v>
+        <v>3980.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2111-11638-CM26</t>
+          <t>1549-3602-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3648,17 +3644,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3668,28 +3664,32 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>4100.35</v>
+        <v>73577.87</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2111-11646-CM26</t>
+          <t>2111-11638-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3744,13 +3744,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2603.4</v>
+        <v>4100.35</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1057049-17460-CM26</t>
+          <t>2111-11646-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3765,22 +3765,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3790,32 +3790,28 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>BLUNDING S.A.</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>79.744.580-0</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.901.400-4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>11343.41</v>
+        <v>2603.4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2069-7602-CM26</t>
+          <t>1057049-17460-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3830,22 +3826,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3855,28 +3851,32 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BLUNDING S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>79.744.580-0</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>7578.59</v>
+        <v>11343.41</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2069-7595-CM26</t>
+          <t>2069-7602-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3931,13 +3931,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>14853.23</v>
+        <v>7578.59</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1171142-2748-CM26</t>
+          <t>2069-7595-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3962,27 +3962,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>62.000.830-3</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3737.1</v>
+        <v>14853.23</v>
       </c>
     </row>
     <row r="58">
@@ -4059,7 +4059,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2069-7593-CM26</t>
+          <t>1171142-2748-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4084,27 +4084,27 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>62.000.830-3</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>19069.59</v>
+        <v>3737.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2080-8391-CM26</t>
+          <t>2069-7593-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4145,27 +4145,27 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>78.073.910-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4175,13 +4175,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>38027.02</v>
+        <v>19069.59</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>812030-890-CM26</t>
+          <t>2080-8391-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4206,47 +4206,43 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>PRODUCTOS MEDICOS LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.073.910-k</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3722.5</v>
+        <v>38027.02</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1549-3689-CM26</t>
+          <t>812030-890-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4266,17 +4262,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4286,28 +4282,32 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>56556.75</v>
+        <v>3722.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057501-9565-CM26</t>
+          <t>1549-3689-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4347,12 +4347,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4362,13 +4362,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>46134.59</v>
+        <v>56556.75</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1057534-1072-CM26</t>
+          <t>1057501-9565-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4393,27 +4393,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4423,13 +4423,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2346.8</v>
+        <v>46134.59</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2111-11754-CM26</t>
+          <t>1057534-1072-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4454,17 +4454,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4484,13 +4484,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2621.92</v>
+        <v>2346.8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3391-543-CM26</t>
+          <t>2048-2421-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4515,43 +4515,47 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.975.800-5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3548.94</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1057049-17540-CM26</t>
+          <t>2111-11754-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4571,17 +4575,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4591,12 +4595,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4606,13 +4610,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2358.69</v>
+        <v>2621.92</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4502-751-CM26</t>
+          <t>3391-543-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4632,52 +4636,48 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>4173.3</v>
+        <v>3548.94</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1422830-162-CM26</t>
+          <t>1057049-17540-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4697,52 +4697,48 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.485.678-3</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>4325.22</v>
+        <v>2358.69</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2048-2421-CM26</t>
+          <t>4502-751-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4762,32 +4758,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.975.800-5</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4801,13 +4797,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2385</v>
+        <v>4173.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1057049-17479-CM26</t>
+          <t>1422830-162-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4832,27 +4828,27 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4866,13 +4862,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3732.64</v>
+        <v>4325.22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3328-2156-CM26</t>
+          <t>1057049-17479-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4897,12 +4893,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4912,28 +4908,32 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>14161.61</v>
+        <v>3732.64</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1641-19028-CM26</t>
+          <t>3328-2156-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.608.204-3</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>4717.64</v>
+        <v>14161.61</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1641-19026-CM26</t>
+          <t>1641-19028-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5049,13 +5049,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>7581.93</v>
+        <v>4717.64</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>812030-798-CM26</t>
+          <t>1641-19026-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.204-3</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5110,13 +5110,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5757.16</v>
+        <v>7581.93</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3378-7297-CM26</t>
+          <t>812030-798-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5171,13 +5171,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>3912.08</v>
+        <v>5757.16</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1947-3865-CM26</t>
+          <t>3378-7297-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.608.004-0</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NORTE HOSPITAL ROBERTO DEL RIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5217,32 +5217,28 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2498.03</v>
+        <v>3912.08</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5083-439-CM26</t>
+          <t>1947-3865-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5267,43 +5263,47 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.608.004-0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD NORTE HOSPITAL ROBERTO DEL RIO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>4886.59</v>
+        <v>2498.03</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1057402-8899-CM26</t>
+          <t>5083-439-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5328,47 +5328,43 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>3749.65</v>
+        <v>4886.59</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1057389-3767-CM26</t>
+          <t>1057402-8899-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5393,43 +5389,47 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2632.04</v>
+        <v>3749.65</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2258-6335-CM26</t>
+          <t>1057389-3767-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5454,27 +5454,27 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5484,13 +5484,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>60794</v>
+        <v>2632.04</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2258-6314-CM26</t>
+          <t>2258-6335-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5545,13 +5545,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>22308.77</v>
+        <v>60794</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2258-6605-CM26</t>
+          <t>2258-6314-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5606,13 +5606,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>5517.44</v>
+        <v>22308.77</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2215-870-CM26</t>
+          <t>2258-6605-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5627,22 +5627,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5667,13 +5667,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>16369.14</v>
+        <v>5517.44</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>812030-895-CM26</t>
+          <t>1704-4716-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5698,17 +5698,17 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5728,13 +5728,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>59644.5</v>
+        <v>14610.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3378-7368-CM26</t>
+          <t>1422824-2750-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5759,27 +5759,27 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5789,13 +5789,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3608.81</v>
+        <v>7546.6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1422824-2750-CM26</t>
+          <t>2215-870-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5820,27 +5820,27 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5850,13 +5850,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>7546.6</v>
+        <v>16369.14</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1704-4716-CM26</t>
+          <t>812030-895-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5881,17 +5881,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5911,13 +5911,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>14610.7</v>
+        <v>59644.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3328-2227-CM26</t>
+          <t>3378-7368-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5957,32 +5957,28 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>8138.68</v>
+        <v>3608.81</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3328-2217-CM26</t>
+          <t>3328-2227-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6002,7 +5998,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6022,28 +6018,32 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2779.07</v>
+        <v>8138.68</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1057539-6878-CM26</t>
+          <t>3328-2217-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6068,27 +6068,27 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -6098,13 +6098,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>60585.44</v>
+        <v>2779.07</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1952-2135-CM26</t>
+          <t>1057539-6878-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6124,32 +6124,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6159,13 +6159,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>14564.55</v>
+        <v>60585.44</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1057402-8592-CM26</t>
+          <t>1952-2133-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6190,27 +6190,27 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6220,13 +6220,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>3784.84</v>
+        <v>5805.23</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1952-2133-CM26</t>
+          <t>1057402-8592-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6251,27 +6251,27 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6281,13 +6281,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>5805.23</v>
+        <v>3784.84</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1057402-8508-CM26</t>
+          <t>1952-2135-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6312,27 +6312,27 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6342,13 +6342,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>5946.43</v>
+        <v>14564.55</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1057402-8336-CM26</t>
+          <t>1057402-8508-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6403,13 +6403,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>4552.93</v>
+        <v>5946.43</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1057402-8334-CM26</t>
+          <t>1057402-8336-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6464,13 +6464,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>5201.68</v>
+        <v>4552.93</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1057402-8322-CM26</t>
+          <t>1057402-8334-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6510,32 +6510,28 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2800.66</v>
+        <v>5201.68</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1057402-8511-CM26</t>
+          <t>1057402-8322-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6575,28 +6571,32 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>4188.09</v>
+        <v>2800.66</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3391-549-CM26</t>
+          <t>1057417-14576-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6611,37 +6611,37 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6651,13 +6651,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2585.36</v>
+        <v>8292.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1549-3800-CM26</t>
+          <t>1057402-8511-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6682,17 +6682,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6712,13 +6712,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>75746.94</v>
+        <v>4188.09</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1549-3801-CM26</t>
+          <t>3391-550-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6743,47 +6743,43 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>69228.87</v>
+        <v>4086.47</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1952-2262-CM26</t>
+          <t>3391-549-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6808,27 +6804,27 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6838,13 +6834,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>15364.28</v>
+        <v>2585.36</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3328-2237-CM26</t>
+          <t>1549-3800-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6869,12 +6865,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6899,13 +6895,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3504.09</v>
+        <v>75746.94</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>5083-455-CM26</t>
+          <t>1549-3801-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6925,48 +6921,52 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>6442.42</v>
+        <v>69228.87</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3391-550-CM26</t>
+          <t>1952-2262-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6991,27 +6991,27 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4086.47</v>
+        <v>15364.28</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1549-3804-CM26</t>
+          <t>3328-2237-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7042,22 +7042,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7067,32 +7067,28 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>9764.559999999999</v>
+        <v>3504.09</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1549-3803-CM26</t>
+          <t>5083-455-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7107,7 +7103,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7117,101 +7113,288 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.485.678-3</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>55550.71</v>
+        <v>6442.42</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>1549-3804-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>9764.559999999999</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2107-1794-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>61.602.148-6</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>TECNOMEDICAL S A</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>99.585.860-6</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>41622.72</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1549-3803-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>61.608.002-4</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>55550.71</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>2109-1794-CM26</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>61.608.203-5</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
         <is>
           <t>SINERMED SPA</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t>76.367.671-4</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="n">
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
         <v>7492.09</v>
       </c>
     </row>
